--- a/audit/docker_benchmark_reports/192.168.1.8_section4.xlsx
+++ b/audit/docker_benchmark_reports/192.168.1.8_section4.xlsx
@@ -104,12 +104,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="009C2B26"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="001A4E8A"/>
       <sz val="10"/>
     </font>
@@ -117,6 +111,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001A6E2E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00666666"/>
       <sz val="10"/>
     </font>
     <font>
@@ -255,7 +255,7 @@
     <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -264,10 +264,10 @@
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -811,7 +811,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Host: Docker-2204-DA-AUTO   |   OS: Ubuntu 22.04   |   Generated: 2026-05-18T05:57:40Z</t>
+          <t>Host: Docker-2204-DA-AUTO   |   OS: Ubuntu 22.04   |   Generated: 2026-05-21T18:49:04Z</t>
         </is>
       </c>
     </row>
@@ -853,26 +853,26 @@
         <v>12</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="10" customHeight="1"/>
     <row r="9" ht="28" customHeight="1">
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Compliance Score:   █████░░░░░░░░░░░░░░░   25.0%  (3 of 12 checks passed)</t>
+          <t xml:space="preserve">  Compliance Score:   █░░░░░░░░░░░░░░░░░░░   8.3%  (1 of 12 checks passed)</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>[FAIL] 4.1 - Containers running as root: c7a07d962204</t>
+          <t>[INFO] 4.1 - No containers running</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
           <t>Ensure containers use only trusted base images</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -954,7 +954,7 @@
           <t>Ensure unnecessary packages are not installed in the container</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -976,7 +976,7 @@
           <t>Ensure images are scanned and rebuilt to include security patches</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -998,7 +998,7 @@
           <t>Ensure Content trust for Docker is Enabled</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1020,14 +1020,14 @@
           <t>Ensure HEALTHCHECK instructions have been added to container images</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
-          <t>[FAIL] 4.6 - Images missing HEALTHCHECK: 6c3a6ea6608c</t>
+          <t>[SKIP] 4.6 - No local images found.</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>[PASS] 4.7 - No standalone update instructions found in image history.</t>
+          <t>[SKIP] 4.7 - No local images found.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
           <t>Ensure setuid and setgid permissions are removed in images</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>[PASS] 4.9 - No ADD instructions found. COPY used correctly.</t>
+          <t>[SKIP] 4.9 - No local images found.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
           <t>Ensure secrets are not stored in Dockerfiles</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1130,7 +1130,7 @@
           <t>Ensure only verified packages are installed in the container</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1152,7 +1152,7 @@
           <t>Ensure all signed artifacts are validated</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>[FAIL] 4.1 - Containers running as root: c7a07d962204</t>
+          <t>[INFO] 4.1 - No containers running</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -1335,7 +1335,7 @@
           <t>Ensure containers use only trusted base images</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1367,7 +1367,7 @@
           <t>Ensure unnecessary packages are not installed in the container</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1399,7 +1399,7 @@
           <t>Ensure images are scanned and rebuilt to include security patches</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1431,7 +1431,7 @@
           <t>Ensure Content trust for Docker is Enabled</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1463,14 +1463,14 @@
           <t>Ensure HEALTHCHECK instructions have been added to container images</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>[FAIL] 4.6 - Images missing HEALTHCHECK: 6c3a6ea6608c</t>
+          <t>[SKIP] 4.6 - No local images found.</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>[PASS] 4.7 - No standalone update instructions found in image history.</t>
+          <t>[SKIP] 4.7 - No local images found.</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -1527,7 +1527,7 @@
           <t>Ensure setuid and setgid permissions are removed in images</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>[PASS] 4.9 - No ADD instructions found. COPY used correctly.</t>
+          <t>[SKIP] 4.9 - No local images found.</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
@@ -1587,7 +1587,7 @@
           <t>Ensure secrets are not stored in Dockerfiles</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1619,7 +1619,7 @@
           <t>Ensure only verified packages are installed in the container</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1651,7 +1651,7 @@
           <t>Ensure all signed artifacts are validated</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1790,14 +1790,14 @@
     <row r="4" ht="14" customHeight="1">
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "fail": 2,</t>
+          <t xml:space="preserve">    "fail": 0,</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "generated": "2026-05-18T05:57:40Z",</t>
+          <t xml:space="preserve">    "generated": "2026-05-21T18:49:04Z",</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
     <row r="7" ht="14" customHeight="1">
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "info": 7,</t>
+          <t xml:space="preserve">    "info": 8,</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
     <row r="9" ht="14" customHeight="1">
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "pass": 3,</t>
+          <t xml:space="preserve">    "pass": 1,</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
     <row r="11" ht="14" customHeight="1">
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "skip": 0,</t>
+          <t xml:space="preserve">    "skip": 3,</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "details": "[FAIL] 4.1 - Containers running as root: c7a07d962204",</t>
+          <t xml:space="preserve">      "details": "[INFO] 4.1 - No containers running",</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
     <row r="21" ht="14" customHeight="1">
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "status": "FAIL",</t>
+          <t xml:space="preserve">      "status": "INFO",</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
     <row r="57" ht="14" customHeight="1">
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "details": "[FAIL] 4.6 - Images missing HEALTHCHECK: 6c3a6ea6608c",</t>
+          <t xml:space="preserve">      "details": "[SKIP] 4.6 - No local images found.",</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
     <row r="61" ht="14" customHeight="1">
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "status": "FAIL",</t>
+          <t xml:space="preserve">      "status": "SKIP",</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
     <row r="65" ht="14" customHeight="1">
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "details": "[PASS] 4.7 - No standalone update instructions found in image history.",</t>
+          <t xml:space="preserve">      "details": "[SKIP] 4.7 - No local images found.",</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
     <row r="69" ht="14" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "status": "PASS",</t>
+          <t xml:space="preserve">      "status": "SKIP",</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
     <row r="80" ht="14" customHeight="1">
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "details": "[PASS] 4.9 - No ADD instructions found. COPY used correctly.",</t>
+          <t xml:space="preserve">      "details": "[SKIP] 4.9 - No local images found.",</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
     <row r="84" ht="14" customHeight="1">
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "status": "PASS",</t>
+          <t xml:space="preserve">      "status": "SKIP",</t>
         </is>
       </c>
     </row>

--- a/audit/docker_benchmark_reports/192.168.1.8_section4.xlsx
+++ b/audit/docker_benchmark_reports/192.168.1.8_section4.xlsx
@@ -104,6 +104,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="009C2B26"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001A4E8A"/>
       <sz val="10"/>
     </font>
@@ -111,12 +117,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001A6E2E"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00666666"/>
       <sz val="10"/>
     </font>
     <font>
@@ -255,7 +255,7 @@
     <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -264,10 +264,10 @@
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -811,7 +811,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Host: Docker-2204-DA-AUTO   |   OS: Ubuntu 22.04   |   Generated: 2026-05-21T18:49:04Z</t>
+          <t>Host: Docker-2204-DA-AUTO   |   OS: Ubuntu 22.04   |   Generated: 2026-05-28T13:04:50Z</t>
         </is>
       </c>
     </row>
@@ -853,26 +853,26 @@
         <v>12</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="10" customHeight="1"/>
     <row r="9" ht="28" customHeight="1">
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Compliance Score:   █░░░░░░░░░░░░░░░░░░░   8.3%  (1 of 12 checks passed)</t>
+          <t xml:space="preserve">  Compliance Score:   █████░░░░░░░░░░░░░░░   25.0%  (3 of 12 checks passed)</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>[INFO] 4.1 - No containers running</t>
+          <t>[FAIL] 4.1 - Containers running as root: 604a9ddde61b</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
           <t>Ensure containers use only trusted base images</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -954,7 +954,7 @@
           <t>Ensure unnecessary packages are not installed in the container</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -976,7 +976,7 @@
           <t>Ensure images are scanned and rebuilt to include security patches</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -998,7 +998,7 @@
           <t>Ensure Content trust for Docker is Enabled</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1020,14 +1020,14 @@
           <t>Ensure HEALTHCHECK instructions have been added to container images</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
-          <t>[SKIP] 4.6 - No local images found.</t>
+          <t>[FAIL] 4.6 - Images missing HEALTHCHECK: 7aaca76c508f</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="H18" s="18" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>[SKIP] 4.7 - No local images found.</t>
+          <t>[PASS] 4.7 - No standalone update instructions found in image history.</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
           <t>Ensure setuid and setgid permissions are removed in images</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>[SKIP] 4.9 - No local images found.</t>
+          <t>[PASS] 4.9 - No ADD instructions found. COPY used correctly.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
           <t>Ensure secrets are not stored in Dockerfiles</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1130,7 +1130,7 @@
           <t>Ensure only verified packages are installed in the container</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1152,7 +1152,7 @@
           <t>Ensure all signed artifacts are validated</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>[INFO] 4.1 - No containers running</t>
+          <t>[FAIL] 4.1 - Containers running as root: 604a9ddde61b</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -1335,7 +1335,7 @@
           <t>Ensure containers use only trusted base images</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1367,7 +1367,7 @@
           <t>Ensure unnecessary packages are not installed in the container</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1399,7 +1399,7 @@
           <t>Ensure images are scanned and rebuilt to include security patches</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1431,7 +1431,7 @@
           <t>Ensure Content trust for Docker is Enabled</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1463,14 +1463,14 @@
           <t>Ensure HEALTHCHECK instructions have been added to container images</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>[SKIP] 4.6 - No local images found.</t>
+          <t>[FAIL] 4.6 - Images missing HEALTHCHECK: 7aaca76c508f</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>[SKIP] 4.7 - No local images found.</t>
+          <t>[PASS] 4.7 - No standalone update instructions found in image history.</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -1527,7 +1527,7 @@
           <t>Ensure setuid and setgid permissions are removed in images</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>[SKIP] 4.9 - No local images found.</t>
+          <t>[PASS] 4.9 - No ADD instructions found. COPY used correctly.</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
@@ -1587,7 +1587,7 @@
           <t>Ensure secrets are not stored in Dockerfiles</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1619,7 +1619,7 @@
           <t>Ensure only verified packages are installed in the container</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1651,7 +1651,7 @@
           <t>Ensure all signed artifacts are validated</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1790,14 +1790,14 @@
     <row r="4" ht="14" customHeight="1">
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "fail": 0,</t>
+          <t xml:space="preserve">    "fail": 2,</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "generated": "2026-05-21T18:49:04Z",</t>
+          <t xml:space="preserve">    "generated": "2026-05-28T13:04:50Z",</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
     <row r="7" ht="14" customHeight="1">
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "info": 8,</t>
+          <t xml:space="preserve">    "info": 7,</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
     <row r="9" ht="14" customHeight="1">
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "pass": 1,</t>
+          <t xml:space="preserve">    "pass": 3,</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
     <row r="11" ht="14" customHeight="1">
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "skip": 3,</t>
+          <t xml:space="preserve">    "skip": 0,</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
     <row r="17" ht="14" customHeight="1">
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "details": "[INFO] 4.1 - No containers running",</t>
+          <t xml:space="preserve">      "details": "[FAIL] 4.1 - Containers running as root: 604a9ddde61b",</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
     <row r="21" ht="14" customHeight="1">
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "status": "INFO",</t>
+          <t xml:space="preserve">      "status": "FAIL",</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
     <row r="57" ht="14" customHeight="1">
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "details": "[SKIP] 4.6 - No local images found.",</t>
+          <t xml:space="preserve">      "details": "[FAIL] 4.6 - Images missing HEALTHCHECK: 7aaca76c508f",</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
     <row r="61" ht="14" customHeight="1">
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "status": "SKIP",</t>
+          <t xml:space="preserve">      "status": "FAIL",</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
     <row r="65" ht="14" customHeight="1">
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "details": "[SKIP] 4.7 - No local images found.",</t>
+          <t xml:space="preserve">      "details": "[PASS] 4.7 - No standalone update instructions found in image history.",</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
     <row r="69" ht="14" customHeight="1">
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "status": "SKIP",</t>
+          <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
     <row r="80" ht="14" customHeight="1">
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "details": "[SKIP] 4.9 - No local images found.",</t>
+          <t xml:space="preserve">      "details": "[PASS] 4.9 - No ADD instructions found. COPY used correctly.",</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
     <row r="84" ht="14" customHeight="1">
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">      "status": "SKIP",</t>
+          <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
